--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/машины ПОКОМ ЗПФ.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/машины ПОКОМ ЗПФ.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28ECB9C4-9E09-40DD-B16C-E485F843DAA9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77184B3A-D427-4837-AEA9-D28500ABF368}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -51,9 +51,6 @@
     <t>ОБЩИИЙ ВЕС</t>
   </si>
   <si>
-    <t>1 машина</t>
-  </si>
-  <si>
     <t>2 машина</t>
   </si>
   <si>
@@ -90,7 +87,10 @@
     <t>Остаток, кор.</t>
   </si>
   <si>
-    <t>Горняк Луганск</t>
+    <t>Вояж Луганск</t>
+  </si>
+  <si>
+    <t>1 машина 19,08</t>
   </si>
 </sst>
 </file>
@@ -121,7 +121,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -140,6 +140,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -598,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -676,6 +682,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -979,29 +987,29 @@
         <v>5</v>
       </c>
       <c r="C1" s="40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1" s="48" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E1" s="49"/>
       <c r="F1" s="48" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1" s="49"/>
       <c r="H1" s="48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1" s="49"/>
       <c r="J1" s="48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K1" s="50"/>
       <c r="L1" s="42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M1" s="38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1009,28 +1017,28 @@
       <c r="B2" s="47"/>
       <c r="C2" s="41"/>
       <c r="D2" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L2" s="43"/>
       <c r="M2" s="39"/>
@@ -1039,8 +1047,12 @@
       <c r="A3" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="24"/>
+      <c r="B3" s="23">
+        <v>3402</v>
+      </c>
+      <c r="C3" s="24">
+        <v>892</v>
+      </c>
       <c r="D3" s="4"/>
       <c r="E3" s="5"/>
       <c r="F3" s="4"/>
@@ -1051,19 +1063,23 @@
       <c r="K3" s="6"/>
       <c r="L3" s="4">
         <f>B3-D3-F3-H3-J3</f>
-        <v>0</v>
+        <v>3402</v>
       </c>
       <c r="M3" s="5">
         <f>C3-E3-G3-I3-K3</f>
-        <v>0</v>
+        <v>892</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="10"/>
+      <c r="B4" s="17">
+        <v>6905</v>
+      </c>
+      <c r="C4" s="10">
+        <v>2098</v>
+      </c>
       <c r="D4" s="2"/>
       <c r="E4" s="3"/>
       <c r="F4" s="2"/>
@@ -1074,21 +1090,29 @@
       <c r="K4" s="7"/>
       <c r="L4" s="2">
         <f t="shared" ref="L4:L11" si="0">B4-D4-F4-H4-J4</f>
-        <v>0</v>
+        <v>6905</v>
       </c>
       <c r="M4" s="3">
         <f t="shared" ref="M4:M11" si="1">C4-E4-G4-I4-K4</f>
-        <v>0</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="3"/>
+      <c r="B5" s="17">
+        <v>7435</v>
+      </c>
+      <c r="C5" s="10">
+        <v>2086</v>
+      </c>
+      <c r="D5" s="17">
+        <v>7435</v>
+      </c>
+      <c r="E5" s="10">
+        <v>2086</v>
+      </c>
       <c r="F5" s="2"/>
       <c r="G5" s="3"/>
       <c r="H5" s="2"/>
@@ -1108,8 +1132,12 @@
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="10"/>
+      <c r="B6" s="17">
+        <v>977</v>
+      </c>
+      <c r="C6" s="10">
+        <v>226</v>
+      </c>
       <c r="D6" s="2"/>
       <c r="E6" s="3"/>
       <c r="F6" s="2"/>
@@ -1120,21 +1148,29 @@
       <c r="K6" s="7"/>
       <c r="L6" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>977</v>
       </c>
       <c r="M6" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="3"/>
+      <c r="A7" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="17">
+        <v>1159</v>
+      </c>
+      <c r="C7" s="10">
+        <v>324</v>
+      </c>
+      <c r="D7" s="17">
+        <v>1159</v>
+      </c>
+      <c r="E7" s="10">
+        <v>324</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="3"/>
       <c r="H7" s="2"/>
@@ -1152,7 +1188,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="14"/>
@@ -1175,7 +1211,7 @@
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="25"/>
       <c r="C9" s="26"/>
@@ -1198,23 +1234,23 @@
     </row>
     <row r="10" spans="1:13" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="21">
         <f>SUM(B3:B9)</f>
-        <v>0</v>
+        <v>19878</v>
       </c>
       <c r="C10" s="21">
         <f>SUM(C3:C9)</f>
-        <v>0</v>
+        <v>5626</v>
       </c>
       <c r="D10" s="15">
         <f>SUM(D3:D9)</f>
-        <v>0</v>
+        <v>8594</v>
       </c>
       <c r="E10" s="16">
         <f t="shared" ref="E10:I10" si="2">SUM(E3:E9)</f>
-        <v>0</v>
+        <v>2410</v>
       </c>
       <c r="F10" s="15">
         <f t="shared" si="2"/>
@@ -1242,16 +1278,16 @@
       </c>
       <c r="L10" s="29">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11284</v>
       </c>
       <c r="M10" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3216</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="32"/>
       <c r="C11" s="33"/>

--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/машины ПОКОМ ЗПФ.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/машины ПОКОМ ЗПФ.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77184B3A-D427-4837-AEA9-D28500ABF368}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCEA42BC-C2A5-4A46-AA12-9082AD2547B0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -643,6 +643,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -682,8 +684,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -980,42 +980,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="48" t="s">
+      <c r="D1" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="49"/>
-      <c r="F1" s="48" t="s">
+      <c r="E1" s="51"/>
+      <c r="F1" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="48" t="s">
+      <c r="G1" s="51"/>
+      <c r="H1" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="49"/>
-      <c r="J1" s="48" t="s">
+      <c r="I1" s="51"/>
+      <c r="J1" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="50"/>
-      <c r="L1" s="42" t="s">
+      <c r="K1" s="52"/>
+      <c r="L1" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="38" t="s">
+      <c r="M1" s="40" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="41"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="43"/>
       <c r="D2" s="8" t="s">
         <v>9</v>
       </c>
@@ -1040,8 +1040,8 @@
       <c r="K2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="43"/>
-      <c r="M2" s="39"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="41"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
@@ -1098,20 +1098,20 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="38" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="17">
-        <v>7435</v>
+        <v>11289</v>
       </c>
       <c r="C5" s="10">
-        <v>2086</v>
+        <v>3152</v>
       </c>
       <c r="D5" s="17">
-        <v>7435</v>
+        <v>11289</v>
       </c>
       <c r="E5" s="10">
-        <v>2086</v>
+        <v>3152</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="3"/>
@@ -1156,7 +1156,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="39" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="17">
@@ -1238,19 +1238,19 @@
       </c>
       <c r="B10" s="21">
         <f>SUM(B3:B9)</f>
-        <v>19878</v>
+        <v>23732</v>
       </c>
       <c r="C10" s="21">
         <f>SUM(C3:C9)</f>
-        <v>5626</v>
+        <v>6692</v>
       </c>
       <c r="D10" s="15">
         <f>SUM(D3:D9)</f>
-        <v>8594</v>
+        <v>12448</v>
       </c>
       <c r="E10" s="16">
         <f t="shared" ref="E10:I10" si="2">SUM(E3:E9)</f>
-        <v>2410</v>
+        <v>3476</v>
       </c>
       <c r="F10" s="15">
         <f t="shared" si="2"/>
